--- a/data/3.10.2/Base_year_2015/extensions/imp_biogeochemical/detail_levels.xlsx
+++ b/data/3.10.2/Base_year_2015/extensions/imp_biogeochemical/detail_levels.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,378 +462,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N - waste - water</t>
+          <t>Pxx - agriculture - soil</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P - waste - water</t>
+          <t>N - waste - water</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NH3 - combustion - air</t>
+          <t>P - waste - water</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NOx - combustion - air</t>
+          <t>NH3 - combustion - air</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SO2 - combustion - air</t>
+          <t>NH3 - non combustion - N- fertilizer production - air</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOx - combustion - air</t>
+          <t>N2O - agriculture - air</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NH3 - non combustion - N- fertilizer production - air</t>
+          <t>NH3 - agriculture - air</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NOx - non combustion - Agglomeration plant - pellets - air</t>
+          <t>NOX - agriculture - air</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOx - non combustion - Agglomeration plant - sinter - air</t>
+          <t>NH3 - waste - air</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NOx - non combustion - Bricks production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Cement production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Chemical wood pulp, dissolving grades - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Chemical wood pulp, soda and sulphate, other than dissolving grades - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Chemical wood pulp, sulphite, other than dissolving grades - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Glass production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Lime production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Nickel, unwrought - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Oil refinery - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Pig iron production, blast furnace - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Production of coke oven coke - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Production of gascoke - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Refined copper; unwrought, not alloyed - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Refined lead, unwrought - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Semi-chemical wood pulp, pulp of fibers other than wood - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Steel production: basic oxygen furnace - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Steel production: electric arc furnace - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Sulphuric acid production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Unrefined copper; copper anodes for electrolytic refining - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NOx - non combustion - Zinc, unwrought, not alloyed - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Agglomeration plant - sinter - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Bricks production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Cement production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Chemical wood pulp, dissolving grades - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Chemical wood pulp, soda and sulphate, other than dissolving grades - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Chemical wood pulp, sulphite, other than dissolving grades - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Glass production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Lime production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Nickel, unwrought - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Oil refinery - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Pig iron production, blast furnace - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Production of coke oven coke - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Production of gascoke - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Refined copper; unwrought, not alloyed - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Refined lead, unwrought - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Semi-chemical wood pulp, pulp of fibers other than wood - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Sulphuric acid production - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Unrefined copper; copper anodes for electrolytic refining - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>SOx - non combustion - Zinc, unwrought, not alloyed - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>N2O - agriculture - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NH3 - agriculture - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NOX - agriculture - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NH3 - waste - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
           <t>NOX - waste - air</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>SOx - waste - air</t>
         </is>
       </c>
     </row>
